--- a/rmonize/data_dictionary/DD_DEGS1_P1.xlsx
+++ b/rmonize/data_dictionary/DD_DEGS1_P1.xlsx
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SOMETHING</t>
+          <t>alkoholfreies Bier ml/Tag</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
